--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104678_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104678_W25.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>H. RUIZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9873</v>
+        <v>0.4693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8867</v>
+        <v>-0.5884</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1006</v>
+        <v>1.0576</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2798</v>
+        <v>-1.1647</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.899</v>
+        <v>-0.402</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3807</v>
+        <v>-0.7627</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.1591</v>
+        <v>-0.8228</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8179</v>
+        <v>-0.7035</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3413</v>
+        <v>-0.1194</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1206</v>
+        <v>-0.3419</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.3014</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0395</v>
+        <v>-0.6433</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.199</v>
+        <v>0.4958</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7924</v>
+        <v>0.2345</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5934</v>
+        <v>0.2614</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4559</v>
+        <v>0.4683</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2429</v>
+        <v>2.0021</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.787</v>
+        <v>-1.5338</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2264</v>
+        <v>-0.2135</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3432</v>
+        <v>2.3545</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5696</v>
+        <v>-2.568</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5101</v>
+        <v>1.4869</v>
       </c>
       <c r="K3" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7365</v>
+        <v>-1.7004</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2652</v>
+        <v>0.2861</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5446</v>
+        <v>-1.5458</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1331</v>
+        <v>-0.3466</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4115</v>
+        <v>-1.1992</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. RUIZ</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0459</v>
+        <v>0.2233</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9354</v>
+        <v>0.3378</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8895</v>
+        <v>-0.1145</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1635</v>
+        <v>-2.2713</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4011</v>
+        <v>-0.8935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7623</v>
+        <v>-1.3778</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8144</v>
+        <v>-1.1853</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6998</v>
+        <v>-0.8348</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1147</v>
+        <v>-0.3505</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.349</v>
+        <v>-1.086</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2986</v>
+        <v>-0.0587</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.0273</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0166</v>
+        <v>-0.5737</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>0.2759</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1043</v>
+        <v>-0.8496</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,22 +799,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6706</v>
+        <v>-0.5359</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0978</v>
+        <v>0.4591</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7684</v>
+        <v>-0.9951</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8445</v>
+        <v>2.1502</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8787</v>
+        <v>4.012</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0343</v>
+        <v>-1.8618</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0543</v>
+        <v>2.5059</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6562</v>
+        <v>4.0851</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6019</v>
+        <v>-1.5793</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7902</v>
+        <v>-0.3557</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2225</v>
+        <v>-0.0731</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5676</v>
+        <v>-0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-2.0032</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0575</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6587</v>
+        <v>-1.3223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2328</v>
+        <v>-0.1508</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0559</v>
+        <v>-0.7993</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1412</v>
+        <v>-0.8384</v>
       </c>
       <c r="H7" t="n">
-        <v>4.007</v>
+        <v>-1.8784</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8658</v>
+        <v>1.04</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5314</v>
+        <v>-0.0827</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1041</v>
+        <v>-1.6762</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5727</v>
+        <v>1.5935</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3902</v>
+        <v>-0.7557</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.2022</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2931</v>
+        <v>-0.5535</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2838</v>
+        <v>-0.8825</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9376</v>
+        <v>-0.156</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3462</v>
+        <v>-0.7265</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5096</v>
+        <v>-1.2411</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.995</v>
+        <v>-0.7619</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5145</v>
+        <v>-0.4793</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3913</v>
+        <v>-1.3909</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.645</v>
+        <v>-0.6462</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.605</v>
+        <v>-0.6012</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3451</v>
+        <v>-0.0779</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3507</v>
+        <v>-3.9952</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3728</v>
+        <v>-2.5152</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9779</v>
+        <v>-1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2548</v>
+        <v>-1.2573</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5124</v>
+        <v>0.5031</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3676</v>
+        <v>-0.3867</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3676</v>
+        <v>-0.3867</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8871</v>
+        <v>-0.8706</v>
       </c>
       <c r="N9" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5677</v>
+        <v>-0.0825</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0998</v>
+        <v>-0.2164</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6675</v>
+        <v>0.1339</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2505</v>
+        <v>-4.2165</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5263</v>
+        <v>-1.5362</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7242</v>
+        <v>-2.6803</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0917</v>
+        <v>-3.0781</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5729</v>
+        <v>-0.5716</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5188</v>
+        <v>-2.5065</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9843</v>
+        <v>-2.0094</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3099</v>
+        <v>-1.3315</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1074</v>
+        <v>-1.0687</v>
       </c>
       <c r="N10" t="n">
-        <v>0.737</v>
+        <v>0.7598</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8444</v>
+        <v>-1.8285</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5725</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5686</v>
+        <v>-0.5464</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0193</v>
+        <v>-1.026</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2945</v>
+        <v>-4.7293</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6011</v>
+        <v>-5.2225</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3066</v>
+        <v>0.4932</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8572</v>
+        <v>-3.8619</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5063</v>
+        <v>-1.5159</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.351</v>
+        <v>-2.3459</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1038</v>
+        <v>-3.1363</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1655</v>
+        <v>-2.1901</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7534</v>
+        <v>-0.7255</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1689</v>
+        <v>-0.5911</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0948</v>
+        <v>-0.6717</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0741</v>
+        <v>0.0805</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.584300000000001</v>
+        <v>-7.8873</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5985</v>
+        <v>-6.1834</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9858</v>
+        <v>-1.7039</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0675</v>
+        <v>-1.0832</v>
       </c>
       <c r="H12" t="n">
-        <v>1.638</v>
+        <v>1.6235</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7055</v>
+        <v>-2.7067</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7936</v>
+        <v>-0.8298</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9311</v>
+        <v>0.9061</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.274</v>
+        <v>-0.2533</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1578</v>
+        <v>-0.4367</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0434</v>
+        <v>-0.5718</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1143</v>
+        <v>0.135</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.4592</v>
+        <v>-22.7669</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.5689</v>
+        <v>-14.1594</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.8902</v>
+        <v>-8.607800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.4087</v>
+        <v>-13.3815</v>
       </c>
       <c r="H13" t="n">
-        <v>2.597599999999999</v>
+        <v>2.585499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-16.0061</v>
+        <v>-15.9669</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.021999999999999</v>
+        <v>-5.2498</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6901000000000004</v>
+        <v>-0.8527999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.3321</v>
+        <v>-4.3974</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.386600000000001</v>
+        <v>-8.131399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>3.287500000000001</v>
+        <v>3.4381</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.6741</v>
+        <v>-11.5697</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1343</v>
+        <v>1.138300000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2075</v>
+        <v>-10.2433</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.939199999999999</v>
+        <v>-7.2701</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3571</v>
+        <v>-2.6516</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.582100000000001</v>
+        <v>-4.6185</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.2457</v>
+        <v>-3.2536</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0175</v>
+        <v>3.9858</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.2631</v>
+        <v>-7.2393</v>
       </c>
     </row>
     <row r="14">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3835</v>
+        <v>7.9931</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8607</v>
+        <v>5.4675</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5227</v>
+        <v>2.5257</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3512</v>
+        <v>5.3359</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4197</v>
+        <v>1.4297</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9314</v>
+        <v>3.9061</v>
       </c>
       <c r="J14" t="n">
-        <v>4.79</v>
+        <v>4.7456</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7928</v>
+        <v>3.7598</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5611</v>
+        <v>0.5903</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8981</v>
+        <v>1.5191</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0707</v>
+        <v>0.7219</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8275</v>
+        <v>0.7972</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0477</v>
+        <v>4.5754</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4574</v>
+        <v>1.205</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5903</v>
+        <v>3.3704</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3153</v>
+        <v>2.3234</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3188</v>
+        <v>0.3242</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9965</v>
+        <v>1.9992</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9197</v>
+        <v>1.9071</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3956</v>
+        <v>0.4164</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9592</v>
+        <v>1.4796</v>
       </c>
       <c r="T15" t="n">
-        <v>0.738</v>
+        <v>0.506</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2212</v>
+        <v>0.9736</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5511</v>
+        <v>4.0444</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5234</v>
+        <v>1.0384</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0277</v>
+        <v>3.006</v>
       </c>
       <c r="G16" t="n">
-        <v>0.535</v>
+        <v>1.0305</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2498</v>
+        <v>-2.1244</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2852</v>
+        <v>3.1548</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5636</v>
+        <v>-0.1611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.377</v>
+        <v>-2.4249</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>2.2638</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0285</v>
+        <v>1.1916</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1272</v>
+        <v>0.3005</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.8911</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>2.725</v>
+        <v>1.4284</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9599</v>
+        <v>0.7521</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7652</v>
+        <v>0.6763</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6105</v>
+        <v>2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5634</v>
+        <v>3.7526</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4926</v>
+        <v>1.9086</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0708</v>
+        <v>1.844</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9563</v>
+        <v>1.4704</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9349</v>
+        <v>-0.3825</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0213</v>
+        <v>1.8529</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3475</v>
+        <v>0.7382</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4648</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1174</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6088</v>
+        <v>0.7322</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4701</v>
+        <v>-0.3168</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1387</v>
+        <v>1.049</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2877</v>
+        <v>0.8466</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2794</v>
+        <v>0.3085</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0083</v>
+        <v>0.538</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.692</v>
+        <v>3.614</v>
       </c>
       <c r="E18" t="n">
-        <v>1.574</v>
+        <v>1.5623</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1181</v>
+        <v>2.0517</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4667</v>
+        <v>0.5266</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3912</v>
+        <v>0.239</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8578</v>
+        <v>0.2876</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7565</v>
+        <v>0.5407</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0591</v>
+        <v>0.3545</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8156</v>
+        <v>0.1862</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3321</v>
+        <v>-0.1155</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0423</v>
+        <v>0.1014</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2017</v>
+        <v>1.7884</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0484</v>
+        <v>1.0217</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1534</v>
+        <v>0.7667</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>0.6162</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4549</v>
+        <v>2.6964</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.083</v>
+        <v>0.88</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5379</v>
+        <v>1.8164</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0522</v>
+        <v>1.9577</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1064</v>
+        <v>1.9385</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1586</v>
+        <v>0.0193</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1139</v>
+        <v>1.3241</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3875</v>
+        <v>1.4511</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2736</v>
+        <v>-0.127</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1661</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2811</v>
+        <v>0.4873</v>
       </c>
       <c r="O19" t="n">
-        <v>0.885</v>
+        <v>0.1463</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1948</v>
+        <v>1.4216</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4325</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2377</v>
+        <v>0.7275</v>
       </c>
       <c r="V19" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4354</v>
+        <v>1.4705</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9827</v>
+        <v>0.9616</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4527</v>
+        <v>0.5089</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3034</v>
+        <v>1.2998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4025</v>
+        <v>0.4048</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9009</v>
+        <v>0.895</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4201</v>
+        <v>0.3952</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0897</v>
+        <v>0.0755</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8833</v>
+        <v>0.9046</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9978</v>
+        <v>1.0325</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5626</v>
+        <v>0.5664</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4352</v>
+        <v>0.4661</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4554</v>
+        <v>1.4675</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7635</v>
+        <v>1.7216</v>
       </c>
       <c r="F21" t="n">
-        <v>2.219</v>
+        <v>-0.2541</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6564</v>
+        <v>3.3362</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3709</v>
+        <v>-0.0922</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7144</v>
+        <v>3.4284</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.942</v>
+        <v>3.4777</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2032</v>
+        <v>0.0377</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2612</v>
+        <v>3.44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2856</v>
+        <v>-0.1416</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8324</v>
+        <v>-0.13</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>-0.0116</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5259</v>
+        <v>-0.2753</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4053</v>
+        <v>-0.3417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1207</v>
+        <v>0.0664</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4132</v>
+        <v>0.8738</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7995</v>
+        <v>1.0323</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3863</v>
+        <v>-0.1585</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.198</v>
+        <v>-0.1901</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7083</v>
+        <v>-0.2532</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3605</v>
+        <v>-0.1416</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3758</v>
+        <v>0.7067</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4091</v>
+        <v>-1.8907</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0333</v>
+        <v>2.5974</v>
       </c>
       <c r="G23" t="n">
-        <v>3.3455</v>
+        <v>-0.6445</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0982</v>
+        <v>-1.3673</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4437</v>
+        <v>0.7228</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5072</v>
+        <v>-1.9531</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0448</v>
+        <v>-2.2138</v>
       </c>
       <c r="L23" t="n">
-        <v>3.4623</v>
+        <v>0.2607</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1617</v>
+        <v>1.3087</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1431</v>
+        <v>0.8465</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0186</v>
+        <v>0.4622</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3819</v>
+        <v>0.7561</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6956</v>
+        <v>0.29</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6863</v>
+        <v>0.4661</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8416</v>
+        <v>-1.8407</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0918</v>
+        <v>-1.0961</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7498</v>
+        <v>-0.7446</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4771</v>
+        <v>-0.4751</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6344</v>
+        <v>-0.633</v>
       </c>
       <c r="J24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0715</v>
+        <v>-3.5209</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2708</v>
+        <v>-4.1828</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1993</v>
+        <v>0.6619</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.5853</v>
+        <v>-2.5895</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.564</v>
+        <v>-2.5702</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0286</v>
+        <v>-3.0491</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2796</v>
+        <v>-2.2967</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4433</v>
+        <v>0.4597</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1016</v>
+        <v>0.6619</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1603</v>
+        <v>0.2808</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0587</v>
+        <v>0.3812</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.4593</v>
+        <v>25.8328</v>
       </c>
       <c r="E26" t="n">
-        <v>8.8903</v>
+        <v>8.607699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>14.5691</v>
+        <v>17.2252</v>
       </c>
       <c r="G26" t="n">
-        <v>13.4088</v>
+        <v>13.3813</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.5976</v>
+        <v>-2.5857</v>
       </c>
       <c r="I26" t="n">
-        <v>16.006</v>
+        <v>15.9669</v>
       </c>
       <c r="J26" t="n">
-        <v>8.386700000000001</v>
+        <v>8.131499999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.2876</v>
+        <v>-3.4383</v>
       </c>
       <c r="L26" t="n">
-        <v>11.6742</v>
+        <v>11.5698</v>
       </c>
       <c r="M26" t="n">
-        <v>5.022099999999999</v>
+        <v>5.249999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6901</v>
+        <v>0.8526999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>4.332000000000001</v>
+        <v>4.3973</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1343</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3417</v>
+        <v>-11.3815</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S26" t="n">
-        <v>7.939000000000002</v>
+        <v>10.336</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5823</v>
+        <v>4.6185</v>
       </c>
       <c r="U26" t="n">
-        <v>3.3569</v>
+        <v>5.717499999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>3.245700000000001</v>
+        <v>3.2535</v>
       </c>
       <c r="W26" t="n">
-        <v>7.263199999999999</v>
+        <v>7.2395</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.0175</v>
+        <v>-3.9858</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104678_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104678_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.2393</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104678_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.9858</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
